--- a/RadarSeparation.xlsx
+++ b/RadarSeparation.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y72"/>
+  <dimension ref="A1:AE72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,92 +466,122 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>LoA TWR Loss</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Radar TMA - Detail</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Radar TMA - Min Dist (nm)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Radar TMA - Altitude (ft)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Radar TMA - Time</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Radar TWR - Detail</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Radar TWR - Min Dist (nm)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Radar TWR - Altitude (ft)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Radar TWR - Time</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Radar TWR - Dist2TWR (nm)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wake TMA - Detail</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Wake TMA - Min Dist (nm)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Wake TMA - Altitude (ft)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Wake TMA - Time</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Wake TWR - Detail</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Wake TWR - Min Dist (nm)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Wake TWR - Altitude (ft)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Wake TWR - Time</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Wake TWR - Dist2TWR (nm)</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>LoA TWR - Detail</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>LoA TWR - Min Dist (nm)</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>LoA TWR - Altitude (ft)</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>LoA TWR - Time</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>LoA TWR - Dist2TWR (nm)</t>
         </is>
       </c>
     </row>
@@ -593,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -677,6 +707,36 @@
         </is>
       </c>
       <c r="Y2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -720,7 +780,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -804,6 +864,36 @@
         </is>
       </c>
       <c r="Y3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -847,7 +937,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,6 +1021,36 @@
         </is>
       </c>
       <c r="Y4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -974,7 +1094,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1058,6 +1178,36 @@
         </is>
       </c>
       <c r="Y5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1101,7 +1251,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1185,6 +1335,36 @@
         </is>
       </c>
       <c r="Y6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1228,7 +1408,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1312,6 +1492,36 @@
         </is>
       </c>
       <c r="Y7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1355,7 +1565,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1439,6 +1649,36 @@
         </is>
       </c>
       <c r="Y8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1482,7 +1722,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1566,6 +1806,36 @@
         </is>
       </c>
       <c r="Y9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1609,7 +1879,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1693,6 +1963,36 @@
         </is>
       </c>
       <c r="Y10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1736,7 +2036,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1820,6 +2120,36 @@
         </is>
       </c>
       <c r="Y11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1863,7 +2193,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1947,6 +2277,36 @@
         </is>
       </c>
       <c r="Y12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1990,7 +2350,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2074,6 +2434,36 @@
         </is>
       </c>
       <c r="Y13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2117,7 +2507,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2201,6 +2591,36 @@
         </is>
       </c>
       <c r="Y14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2244,7 +2664,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2328,6 +2748,36 @@
         </is>
       </c>
       <c r="Y15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2371,7 +2821,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2455,6 +2905,36 @@
         </is>
       </c>
       <c r="Y16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2498,7 +2978,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2582,6 +3062,36 @@
         </is>
       </c>
       <c r="Y17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2625,7 +3135,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2709,6 +3219,36 @@
         </is>
       </c>
       <c r="Y18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2752,7 +3292,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2836,6 +3376,36 @@
         </is>
       </c>
       <c r="Y19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2879,7 +3449,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2963,6 +3533,36 @@
         </is>
       </c>
       <c r="Y20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3006,7 +3606,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3090,6 +3690,36 @@
         </is>
       </c>
       <c r="Y21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3133,7 +3763,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3217,6 +3847,36 @@
         </is>
       </c>
       <c r="Y22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3260,7 +3920,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3344,6 +4004,36 @@
         </is>
       </c>
       <c r="Y23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3387,7 +4077,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3471,6 +4161,36 @@
         </is>
       </c>
       <c r="Y24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3514,7 +4234,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3598,6 +4318,36 @@
         </is>
       </c>
       <c r="Y25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3641,7 +4391,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3725,6 +4475,36 @@
         </is>
       </c>
       <c r="Y26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3768,7 +4548,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3852,6 +4632,36 @@
         </is>
       </c>
       <c r="Y27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3895,7 +4705,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3979,6 +4789,36 @@
         </is>
       </c>
       <c r="Y28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4022,7 +4862,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4106,6 +4946,36 @@
         </is>
       </c>
       <c r="Y29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4149,7 +5019,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4233,6 +5103,36 @@
         </is>
       </c>
       <c r="Y30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4276,7 +5176,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4360,6 +5260,36 @@
         </is>
       </c>
       <c r="Y31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4403,7 +5333,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4487,6 +5417,36 @@
         </is>
       </c>
       <c r="Y32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4530,7 +5490,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4614,6 +5574,36 @@
         </is>
       </c>
       <c r="Y33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4657,7 +5647,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4741,6 +5731,36 @@
         </is>
       </c>
       <c r="Y34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4784,23 +5804,23 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>2.702511764609751</v>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>2000.000324466611</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>19234</v>
       </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>-</t>
@@ -4862,6 +5882,36 @@
         </is>
       </c>
       <c r="Y35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4905,23 +5955,23 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>2.853439522570909</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>1924.997726046532</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>19306</v>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>-</t>
@@ -4983,6 +6033,36 @@
         </is>
       </c>
       <c r="Y36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5026,7 +6106,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -5110,6 +6190,36 @@
         </is>
       </c>
       <c r="Y37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5153,7 +6263,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -5237,6 +6347,36 @@
         </is>
       </c>
       <c r="Y38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5280,23 +6420,23 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>2.874717412781841</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>1749.997660032503</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>19553</v>
       </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>-</t>
@@ -5358,6 +6498,36 @@
         </is>
       </c>
       <c r="Y39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5401,7 +6571,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -5485,6 +6655,36 @@
         </is>
       </c>
       <c r="Y40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5528,7 +6728,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5612,6 +6812,36 @@
         </is>
       </c>
       <c r="Y41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5655,7 +6885,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5739,6 +6969,36 @@
         </is>
       </c>
       <c r="Y42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5782,7 +7042,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5866,6 +7126,36 @@
         </is>
       </c>
       <c r="Y43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5909,7 +7199,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5993,6 +7283,36 @@
         </is>
       </c>
       <c r="Y44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6036,7 +7356,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -6120,6 +7440,36 @@
         </is>
       </c>
       <c r="Y45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6163,23 +7513,23 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I46" t="n">
+      <c r="J46" t="n">
         <v>2.959605396338371</v>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>2075.001877293742</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>20149</v>
       </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>-</t>
@@ -6241,6 +7591,36 @@
         </is>
       </c>
       <c r="Y46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6284,7 +7664,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -6368,6 +7748,36 @@
         </is>
       </c>
       <c r="Y47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6411,7 +7821,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -6495,6 +7905,36 @@
         </is>
       </c>
       <c r="Y48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6538,7 +7978,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -6622,6 +8062,36 @@
         </is>
       </c>
       <c r="Y49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6665,7 +8135,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -6749,6 +8219,36 @@
         </is>
       </c>
       <c r="Y50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6792,23 +8292,23 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="J51" t="n">
         <v>2.914363131315263</v>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>1874.999057547935</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>20588</v>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>-</t>
@@ -6870,6 +8370,36 @@
         </is>
       </c>
       <c r="Y51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6913,23 +8443,23 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
         <v>2.883554209681913</v>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>1675.000088148887</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>20656</v>
       </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>-</t>
@@ -6991,6 +8521,36 @@
         </is>
       </c>
       <c r="Y52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7034,23 +8594,23 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I53" t="n">
+      <c r="J53" t="n">
         <v>2.969562907516054</v>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>1725.000001194534</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>20728</v>
       </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>-</t>
@@ -7112,6 +8672,36 @@
         </is>
       </c>
       <c r="Y53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7155,7 +8745,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -7239,6 +8829,36 @@
         </is>
       </c>
       <c r="Y54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7282,7 +8902,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7366,6 +8986,36 @@
         </is>
       </c>
       <c r="Y55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7409,7 +9059,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -7493,6 +9143,36 @@
         </is>
       </c>
       <c r="Y56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7536,7 +9216,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -7620,6 +9300,36 @@
         </is>
       </c>
       <c r="Y57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7663,23 +9373,23 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I58" t="n">
+      <c r="J58" t="n">
         <v>2.52260092499438</v>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>1631.24375217789</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>21135</v>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>-</t>
@@ -7741,6 +9451,36 @@
         </is>
       </c>
       <c r="Y58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7784,7 +9524,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -7868,6 +9608,36 @@
         </is>
       </c>
       <c r="Y59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -7911,7 +9681,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -7995,6 +9765,36 @@
         </is>
       </c>
       <c r="Y60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8038,23 +9838,23 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="J61" t="n">
         <v>2.885882894370939</v>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>1849.998819064758</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>21371</v>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>-</t>
@@ -8116,6 +9916,36 @@
         </is>
       </c>
       <c r="Y61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8159,7 +9989,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -8243,6 +10073,36 @@
         </is>
       </c>
       <c r="Y62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8286,7 +10146,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -8370,6 +10230,36 @@
         </is>
       </c>
       <c r="Y63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8413,23 +10303,23 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I64" t="n">
+      <c r="J64" t="n">
         <v>2.551067874205077</v>
       </c>
-      <c r="J64" t="n">
+      <c r="K64" t="n">
         <v>1749.997736604608</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>21603</v>
       </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>-</t>
@@ -8491,6 +10381,36 @@
         </is>
       </c>
       <c r="Y64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8534,7 +10454,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -8621,6 +10541,28 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>LOA LOSS OF SEPARATION</t>
+        </is>
+      </c>
+      <c r="AB65" t="n">
+        <v>4.278610602058058</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>3025.023761812851</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>21743</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>0.6504649552425935</v>
       </c>
     </row>
     <row r="66">
@@ -8661,7 +10603,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -8745,6 +10687,36 @@
         </is>
       </c>
       <c r="Y66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8788,7 +10760,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8872,6 +10844,36 @@
         </is>
       </c>
       <c r="Y67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -8915,23 +10917,23 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
           <t>HORIZONTAL SEPARATION</t>
         </is>
       </c>
-      <c r="I68" t="n">
+      <c r="J68" t="n">
         <v>2.827901884027331</v>
       </c>
-      <c r="J68" t="n">
+      <c r="K68" t="n">
         <v>1724.996033157541</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>21918</v>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>-</t>
@@ -8993,6 +10995,36 @@
         </is>
       </c>
       <c r="Y68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9036,7 +11068,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -9123,6 +11155,28 @@
         <is>
           <t>-</t>
         </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>LOA LOSS OF SEPARATION</t>
+        </is>
+      </c>
+      <c r="AB69" t="n">
+        <v>4.783158337568745</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>2450.036629410697</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>22042</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.5406857511061068</v>
       </c>
     </row>
     <row r="70">
@@ -9163,7 +11217,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -9247,6 +11301,36 @@
         </is>
       </c>
       <c r="Y70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9290,7 +11374,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -9374,6 +11458,36 @@
         </is>
       </c>
       <c r="Y71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9417,7 +11531,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9501,6 +11615,36 @@
         </is>
       </c>
       <c r="Y72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/RadarSeparation.xlsx
+++ b/RadarSeparation.xlsx
@@ -583,7 +583,7 @@
         <v>8.773637125929048</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q2" t="n">
         <v>3620.281073161436</v>
@@ -657,7 +657,7 @@
         <v>6.188205438717591</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q3" t="n">
         <v>2568.821135002041</v>
@@ -731,7 +731,7 @@
         <v>6.764160240530157</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q4" t="n">
         <v>5034.965146426352</v>
@@ -805,7 +805,7 @@
         <v>5.595231357403071</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q5" t="n">
         <v>3096.665451579348</v>
@@ -879,7 +879,7 @@
         <v>5.534080356031083</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q6" t="n">
         <v>2748.38285915433</v>
@@ -953,7 +953,7 @@
         <v>4.546314068276478</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" t="n">
         <v>2461.746954742964</v>
@@ -1027,7 +1027,7 @@
         <v>5.806694157981677</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q8" t="n">
         <v>2881.208240549883</v>
@@ -1101,7 +1101,7 @@
         <v>5.872458038059335</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q9" t="n">
         <v>4474.814509835956</v>
@@ -1175,7 +1175,7 @@
         <v>5.407894675713457</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q10" t="n">
         <v>2855.443111468849</v>
@@ -1249,7 +1249,7 @@
         <v>4.503266333807015</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" t="n">
         <v>2293.332029719426</v>
@@ -1315,7 +1315,7 @@
         <v>10.58936238927307</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q12" t="n">
         <v>7806.486706874188</v>
@@ -1389,7 +1389,7 @@
         <v>5.982933333820198</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q13" t="n">
         <v>3329.009676600119</v>
@@ -1463,7 +1463,7 @@
         <v>6.353294800544236</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q14" t="n">
         <v>4420.051637189189</v>
@@ -1537,7 +1537,7 @@
         <v>4.948139942837459</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q15" t="n">
         <v>3069.895479392388</v>
@@ -1611,7 +1611,7 @@
         <v>5.322340678774827</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q16" t="n">
         <v>2600.011714745887</v>
@@ -1677,7 +1677,7 @@
         <v>5.621240373777285</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q17" t="n">
         <v>4843.310397846863</v>
@@ -1751,7 +1751,7 @@
         <v>4.850408902035884</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q18" t="n">
         <v>2561.280941328275</v>
@@ -1825,7 +1825,7 @@
         <v>5.875632483026255</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q19" t="n">
         <v>2888.514769119996</v>
@@ -1899,7 +1899,7 @@
         <v>7.638274582772553</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q20" t="n">
         <v>4369.218602597286</v>
@@ -1973,7 +1973,7 @@
         <v>4.643489412115283</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q21" t="n">
         <v>2476.22026030425</v>
@@ -2047,7 +2047,7 @@
         <v>6.485641188937064</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q22" t="n">
         <v>2667.128768143225</v>
@@ -2121,7 +2121,7 @@
         <v>7.549016481333314</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q23" t="n">
         <v>3823.152172915248</v>
@@ -2187,7 +2187,7 @@
         <v>18.99251701387163</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q24" t="n">
         <v>13054.48714363916</v>
@@ -2253,7 +2253,7 @@
         <v>14.83171854048441</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q25" t="n">
         <v>10950.7200594625</v>
@@ -2319,7 +2319,7 @@
         <v>8.60174057237732</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q26" t="n">
         <v>7816.700801354066</v>
@@ -2385,7 +2385,7 @@
         <v>19.35837255900584</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q27" t="n">
         <v>14975.70642134658</v>
@@ -2451,7 +2451,7 @@
         <v>10.56001636914746</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -2515,7 +2515,7 @@
         <v>17.21172945080025</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q29" t="n">
         <v>10267.85671534743</v>
@@ -2587,7 +2587,7 @@
         <v>5.367210993370685</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -2659,7 +2659,7 @@
         <v>5.622745361009136</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q31" t="n">
         <v>2275.132486603803</v>
@@ -2733,7 +2733,7 @@
         <v>3.951043164932135</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q32" t="n">
         <v>3590.607171739841</v>
@@ -2807,7 +2807,7 @@
         <v>4.112596652023546</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q33" t="n">
         <v>1420.052596834158</v>
@@ -2881,7 +2881,7 @@
         <v>3.780948906655723</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q34" t="n">
         <v>2116.458580716718</v>
@@ -2955,7 +2955,7 @@
         <v>3.650480445241904</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q35" t="n">
         <v>1817.00352296109</v>
@@ -3029,7 +3029,7 @@
         <v>4.857614377691482</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q36" t="n">
         <v>3125.03285344732</v>
@@ -3103,7 +3103,7 @@
         <v>4.824619167676413</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q37" t="n">
         <v>3206.721852474182</v>
@@ -3177,7 +3177,7 @@
         <v>3.857990837093377</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q38" t="n">
         <v>1603.017139515698</v>
@@ -3251,7 +3251,7 @@
         <v>5.56812230228796</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q39" t="n">
         <v>2848.742137512773</v>
@@ -3325,7 +3325,7 @@
         <v>4.48962284566934</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q40" t="n">
         <v>1939.304262816515</v>
@@ -3399,7 +3399,7 @@
         <v>5.667871548392847</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q41" t="n">
         <v>2656.813783798574</v>
@@ -3465,7 +3465,7 @@
         <v>5.805975023196801</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q42" t="n">
         <v>3721.762636722081</v>
@@ -3531,7 +3531,7 @@
         <v>4.124347824935252</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q43" t="n">
         <v>1998.517469002383</v>
@@ -3605,7 +3605,7 @@
         <v>3.991184292725319</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q44" t="n">
         <v>2095.17166970355</v>
@@ -3679,7 +3679,7 @@
         <v>3.860378978369986</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q45" t="n">
         <v>1866.651909683856</v>
@@ -3753,7 +3753,7 @@
         <v>5.786357054594571</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q46" t="n">
         <v>3579.254950614478</v>
@@ -3827,7 +3827,7 @@
         <v>5.533705813538385</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q47" t="n">
         <v>2885.875056065668</v>
@@ -3901,7 +3901,7 @@
         <v>4.455252538810387</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q48" t="n">
         <v>1337.453392198467</v>
@@ -3975,7 +3975,7 @@
         <v>5.872083012711612</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q49" t="n">
         <v>3821.732870999234</v>
@@ -4049,7 +4049,7 @@
         <v>3.623140689178709</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q50" t="n">
         <v>1636.397751006394</v>
@@ -4123,7 +4123,7 @@
         <v>3.976563956729924</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q51" t="n">
         <v>1866.415261095229</v>
@@ -4197,7 +4197,7 @@
         <v>3.911731439487217</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q52" t="n">
         <v>2698.56229100568</v>
@@ -4271,7 +4271,7 @@
         <v>4.017921902036949</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q53" t="n">
         <v>1805.847311815819</v>
@@ -4345,7 +4345,7 @@
         <v>5.492453731270511</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q54" t="n">
         <v>2597.189049509203</v>
@@ -4419,7 +4419,7 @@
         <v>4.081867939013645</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q55" t="n">
         <v>2164.372375258797</v>
@@ -4493,7 +4493,7 @@
         <v>6.26584955175126</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q56" t="n">
         <v>3479.497174798933</v>
@@ -4567,7 +4567,7 @@
         <v>3.241426660720493</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q57" t="n">
         <v>1715.162683711208</v>
@@ -4639,7 +4639,7 @@
         <v>4.905766007393035</v>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
@@ -4711,7 +4711,7 @@
         <v>4.390820103969347</v>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q59" t="n">
         <v>2345.022471251741</v>
@@ -4785,7 +4785,7 @@
         <v>3.745346442226908</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
@@ -4857,7 +4857,7 @@
         <v>5.11578298245241</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q61" t="n">
         <v>3276.196329794571</v>
@@ -4931,7 +4931,7 @@
         <v>4.548553283365578</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
@@ -5003,7 +5003,7 @@
         <v>3.324498844707619</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q63" t="n">
         <v>1925.070657404491</v>
@@ -5077,7 +5077,7 @@
         <v>4.246056090554172</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q64" t="n">
         <v>3070.214301018874</v>
@@ -5151,7 +5151,7 @@
         <v>4.56045972170778</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q65" t="n">
         <v>2162.705467055987</v>
@@ -5225,7 +5225,7 @@
         <v>4.196303521158117</v>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q66" t="n">
         <v>1978.119549624547</v>
@@ -5299,7 +5299,7 @@
         <v>3.827904010745061</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q67" t="n">
         <v>2319.914589190835</v>
@@ -5373,7 +5373,7 @@
         <v>4.77448126077643</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q68" t="n">
         <v>2439.160070368576</v>
@@ -5447,7 +5447,7 @@
         <v>4.753478985811091</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q69" t="n">
         <v>3017.588237808717</v>
@@ -5521,7 +5521,7 @@
         <v>6.125219515616166</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q70" t="n">
         <v>3861.290128105628</v>
@@ -5595,7 +5595,7 @@
         <v>6.070820738236529</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q71" t="n">
         <v>4575.011507975029</v>
@@ -5669,7 +5669,7 @@
         <v>3.877299993693755</v>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q72" t="n">
         <v>2663.761158410617</v>
@@ -5743,7 +5743,7 @@
         <v>4.652684370068189</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q73" t="n">
         <v>2031.869646984498</v>
@@ -5817,7 +5817,7 @@
         <v>3.544200715742492</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q74" t="n">
         <v>1835.824019466443</v>
@@ -5891,7 +5891,7 @@
         <v>4.505848836325718</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q75" t="n">
         <v>1873.124539617948</v>
@@ -5957,7 +5957,7 @@
         <v>11.54048720384428</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q76" t="n">
         <v>7993.022027145769</v>
@@ -6031,7 +6031,7 @@
         <v>5.091992253319329</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q77" t="n">
         <v>3537.477605795105</v>
@@ -6105,7 +6105,7 @@
         <v>4.770289090981912</v>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q78" t="n">
         <v>2302.559300333876</v>
@@ -6179,7 +6179,7 @@
         <v>8.130794134857354</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q79" t="n">
         <v>4653.48823325286</v>
@@ -6253,7 +6253,7 @@
         <v>6.531934832615485</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q80" t="n">
         <v>2437.851859320508</v>
@@ -6327,7 +6327,7 @@
         <v>4.756816180152658</v>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q81" t="n">
         <v>2792.781275024198</v>
@@ -6401,7 +6401,7 @@
         <v>6.243419129208053</v>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q82" t="n">
         <v>2890.568018253165</v>
@@ -6475,7 +6475,7 @@
         <v>6.217966200635963</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q83" t="n">
         <v>4522.451610627212</v>
@@ -6549,7 +6549,7 @@
         <v>4.261480341091596</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q84" t="n">
         <v>1473.521451456588</v>
@@ -6615,7 +6615,7 @@
         <v>37.41076996100543</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q85" t="n">
         <v>29029.5686546914</v>
@@ -6681,7 +6681,7 @@
         <v>6.88097280634908</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q86" t="n">
         <v>5112.348556225783</v>
@@ -6747,7 +6747,7 @@
         <v>9.532071976676812</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q87" t="n">
         <v>5745.408523189255</v>
@@ -6821,7 +6821,7 @@
         <v>6.946164193986857</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q88" t="n">
         <v>4039.010865980704</v>
@@ -6895,7 +6895,7 @@
         <v>6.517339405767062</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q89" t="n">
         <v>3228.993168913027</v>
@@ -6969,7 +6969,7 @@
         <v>3.816568987320708</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q90" t="n">
         <v>1978.363041750179</v>
@@ -7043,7 +7043,7 @@
         <v>5.093441544317968</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q91" t="n">
         <v>2839.374080892851</v>
@@ -7117,7 +7117,7 @@
         <v>5.470129057825526</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q92" t="n">
         <v>3078.309411513685</v>
@@ -7183,7 +7183,7 @@
         <v>27.70303273102304</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q93" t="n">
         <v>18724.42392011629</v>
@@ -7257,7 +7257,7 @@
         <v>5.474829877423945</v>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q94" t="n">
         <v>2369.187867016654</v>
@@ -7331,7 +7331,7 @@
         <v>5.7430678787302</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q95" t="n">
         <v>2849.406613925066</v>
@@ -7397,7 +7397,7 @@
         <v>15.38607608225034</v>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q96" t="n">
         <v>12833.15444210844</v>
@@ -7471,7 +7471,7 @@
         <v>5.758127947888689</v>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q97" t="n">
         <v>2981.150509081503</v>
@@ -7545,7 +7545,7 @@
         <v>3.918232073722256</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q98" t="n">
         <v>1674.073422191074</v>
@@ -7619,7 +7619,7 @@
         <v>5.81874615140462</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q99" t="n">
         <v>3445.981281148013</v>
@@ -7693,7 +7693,7 @@
         <v>3.832435817535283</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q100" t="n">
         <v>2175.736563990438</v>
@@ -7759,7 +7759,7 @@
         <v>18.59659885672986</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q101" t="n">
         <v>66895.94417845955</v>
@@ -7833,7 +7833,7 @@
         <v>5.026937648058869</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q102" t="n">
         <v>3269.741090812225</v>
@@ -7907,7 +7907,7 @@
         <v>8.04989772365426</v>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q103" t="n">
         <v>2752.43385046948</v>
@@ -7973,7 +7973,7 @@
         <v>6.167178506328621</v>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q104" t="n">
         <v>5812.772450726096</v>
@@ -8047,7 +8047,7 @@
         <v>4.283569991853439</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q105" t="n">
         <v>2183.855455171256</v>
@@ -8113,7 +8113,7 @@
         <v>5.458747931967979</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q106" t="n">
         <v>2867.263394085484</v>
@@ -8179,7 +8179,7 @@
         <v>5.050037051585375</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q107" t="n">
         <v>2929.262171011406</v>
@@ -8253,7 +8253,7 @@
         <v>6.368879213056079</v>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q108" t="n">
         <v>3909.901724406096</v>
@@ -8319,7 +8319,7 @@
         <v>12.92683526310222</v>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q109" t="n">
         <v>8321.694843742804</v>
@@ -8393,7 +8393,7 @@
         <v>5.632456073133972</v>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q110" t="n">
         <v>3096.078285076505</v>
@@ -8467,7 +8467,7 @@
         <v>5.482307342910589</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q111" t="n">
         <v>3466.901402590073</v>
@@ -8541,7 +8541,7 @@
         <v>4.163074437719279</v>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q112" t="n">
         <v>2405.683541346745</v>
@@ -8615,7 +8615,7 @@
         <v>7.625488947801215</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q113" t="n">
         <v>3829.450633867101</v>
@@ -8689,7 +8689,7 @@
         <v>6.116691645125452</v>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q114" t="n">
         <v>4182.457946118417</v>
@@ -8755,7 +8755,7 @@
         <v>12.71299663477823</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q115" t="n">
         <v>6941.01811196804</v>
@@ -8829,7 +8829,7 @@
         <v>4.252799092364027</v>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q116" t="n">
         <v>1662.390470744966</v>
@@ -8903,7 +8903,7 @@
         <v>6.172882528447686</v>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q117" t="n">
         <v>3702.90811295111</v>
@@ -8977,7 +8977,7 @@
         <v>4.25534751062803</v>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q118" t="n">
         <v>2366.369238485157</v>
@@ -9043,7 +9043,7 @@
         <v>17.88979168922451</v>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="Q119" t="n">
         <v>10913.28158221424</v>

--- a/RadarSeparation.xlsx
+++ b/RadarSeparation.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,92 +429,92 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Leader</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Sid_lead</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Sid_lead_G</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Follower</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Sid_foll</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sid_foll_G</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Runway</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>TMA loss</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>TWR loss</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>TMA_Type</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>TMA_Dist</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TMA_Alt</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>TWR_Type</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>TWR_Dist</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Dist2TWR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TWR_Alt</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
